--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96844888</v>
+        <v>137237179</v>
       </c>
       <c r="B3" t="n">
-        <v>87368</v>
+        <v>87401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720195</v>
+        <v>720056</v>
       </c>
       <c r="R3" t="n">
-        <v>6418206</v>
+        <v>6418185</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +877,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844888</t>
+          <t>https://artportalen.se/Sighting/137237179</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96844938</v>
+        <v>137237193</v>
       </c>
       <c r="B4" t="n">
-        <v>79837</v>
+        <v>87611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +905,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1026</v>
+        <v>433</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720087</v>
+        <v>720195</v>
       </c>
       <c r="R4" t="n">
-        <v>6418153</v>
+        <v>6418157</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +955,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +985,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844938</t>
+          <t>https://artportalen.se/Sighting/137237193</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96844939</v>
+        <v>96844888</v>
       </c>
       <c r="B5" t="n">
-        <v>79837</v>
+        <v>87368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1026</v>
+        <v>449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720102</v>
+        <v>720195</v>
       </c>
       <c r="R5" t="n">
-        <v>6418150</v>
+        <v>6418206</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1082,16 +1098,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844939</t>
+          <t>https://artportalen.se/Sighting/96844888</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96844866</v>
+        <v>137240150</v>
       </c>
       <c r="B6" t="n">
-        <v>75336</v>
+        <v>87497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1115,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1116</v>
+        <v>473</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720093</v>
+        <v>720064</v>
       </c>
       <c r="R6" t="n">
-        <v>6418136</v>
+        <v>6418169</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1169,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,49 +1199,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844866</t>
+          <t>https://artportalen.se/Sighting/137240150</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96844921</v>
+        <v>96844938</v>
       </c>
       <c r="B7" t="n">
-        <v>90663</v>
+        <v>79837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1595</v>
+        <v>1026</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720190</v>
+        <v>720087</v>
       </c>
       <c r="R7" t="n">
-        <v>6418114</v>
+        <v>6418153</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1286,38 +1312,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844921</t>
+          <t>https://artportalen.se/Sighting/96844938</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96844877</v>
+        <v>96844939</v>
       </c>
       <c r="B8" t="n">
-        <v>91329</v>
+        <v>79837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4191</v>
+        <v>1026</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720205</v>
+        <v>720102</v>
       </c>
       <c r="R8" t="n">
-        <v>6418151</v>
+        <v>6418150</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,16 +1414,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844877</t>
+          <t>https://artportalen.se/Sighting/96844939</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96844899</v>
+        <v>96844866</v>
       </c>
       <c r="B9" t="n">
-        <v>87346</v>
+        <v>75336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>1116</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720160</v>
+        <v>720093</v>
       </c>
       <c r="R9" t="n">
-        <v>6418181</v>
+        <v>6418136</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1490,7 +1516,5398 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/96844866</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>96844921</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90663</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>720190</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6418114</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844921</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137237189</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>720160</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6418175</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237189</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137239872</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>720183</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6418166</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239872</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137239874</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>720205</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6418184</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239874</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137239997</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>720171</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6418150</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239997</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137239999</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>720200</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6418166</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239999</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137240009</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>720160</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6418179</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240009</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137237180</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91924</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>720071</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6418186</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237180</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137237259</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96601</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>720125</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6418174</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237259</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137237191</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91576</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>720160</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6418178</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237191</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137237258</v>
+      </c>
+      <c r="B20" t="n">
+        <v>87517</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>720154</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6418199</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237258</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137239866</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>720051</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6418177</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239866</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137239867</v>
+      </c>
+      <c r="B22" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>720120</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6418133</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239867</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137239864</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91537</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>720048</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6418177</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239864</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137239869</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91537</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>720155</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6418130</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239869</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137239994</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91537</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>720135</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6418121</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239994</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137240171</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91537</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>720159</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6418114</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240171</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>96844877</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91329</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4191</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Geastrum michelianum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>720205</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6418151</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844877</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137239865</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4191</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Geastrum michelianum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>720051</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6418177</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239865</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137239876</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4191</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Geastrum michelianum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>720202</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6418171</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239876</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137239996</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4191</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Geastrum michelianum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>720183</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6418149</v>
+      </c>
+      <c r="S30" t="n">
+        <v>11</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239996</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137237185</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93435</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>720136</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6418135</v>
+      </c>
+      <c r="S31" t="n">
+        <v>9</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237185</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137239879</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93435</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>720201</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6418193</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Stor halvcirkel i löv/barrmatta under gran och hassel</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239879</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137240010</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93477</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>720148</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6418164</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240010</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137237186</v>
+      </c>
+      <c r="B34" t="n">
+        <v>111687</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>720139</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6418142</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237186</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137239882</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>720063</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6418152</v>
+      </c>
+      <c r="S35" t="n">
+        <v>13</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239882</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137237181</v>
+      </c>
+      <c r="B36" t="n">
+        <v>102515</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>720131</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6418123</v>
+      </c>
+      <c r="S36" t="n">
+        <v>9</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237181</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137237182</v>
+      </c>
+      <c r="B37" t="n">
+        <v>102515</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>720151</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6418130</v>
+      </c>
+      <c r="S37" t="n">
+        <v>9</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237182</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137237188</v>
+      </c>
+      <c r="B38" t="n">
+        <v>102515</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>720138</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6418145</v>
+      </c>
+      <c r="S38" t="n">
+        <v>9</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237188</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137237257</v>
+      </c>
+      <c r="B39" t="n">
+        <v>102515</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>720127</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6418141</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237257</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137237176</v>
+      </c>
+      <c r="B40" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>720035</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6418184</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237176</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137240154</v>
+      </c>
+      <c r="B41" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>720138</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6418133</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240154</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137237178</v>
+      </c>
+      <c r="B42" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>720052</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6418183</v>
+      </c>
+      <c r="S42" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237178</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137237190</v>
+      </c>
+      <c r="B43" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>720160</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6418176</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237190</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137237260</v>
+      </c>
+      <c r="B44" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>720065</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6418154</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237260</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137237261</v>
+      </c>
+      <c r="B45" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>720051</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6418162</v>
+      </c>
+      <c r="S45" t="n">
+        <v>7</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237261</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137237262</v>
+      </c>
+      <c r="B46" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>720034</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6418163</v>
+      </c>
+      <c r="S46" t="n">
+        <v>9</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237262</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137239881</v>
+      </c>
+      <c r="B47" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>720152</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6418189</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239881</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137240151</v>
+      </c>
+      <c r="B48" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>720062</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6418146</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240151</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137240152</v>
+      </c>
+      <c r="B49" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>720059</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6418149</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240152</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137240153</v>
+      </c>
+      <c r="B50" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>720059</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6418142</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240153</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>96844899</v>
+      </c>
+      <c r="B51" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>720160</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6418181</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/96844899</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137240155</v>
+      </c>
+      <c r="B52" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>720146</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6418153</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240155</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137239870</v>
+      </c>
+      <c r="B53" t="n">
+        <v>93455</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>720172</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6418159</v>
+      </c>
+      <c r="S53" t="n">
+        <v>6</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239870</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137239995</v>
+      </c>
+      <c r="B54" t="n">
+        <v>93455</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>720134</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6418126</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ej skarp smak</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239995</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137240000</v>
+      </c>
+      <c r="B55" t="n">
+        <v>93455</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>720174</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6418161</v>
+      </c>
+      <c r="S55" t="n">
+        <v>6</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ej skarp smak</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240000</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137239871</v>
+      </c>
+      <c r="B56" t="n">
+        <v>93469</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>720191</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6418148</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239871</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137240002</v>
+      </c>
+      <c r="B57" t="n">
+        <v>93469</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>720178</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6418157</v>
+      </c>
+      <c r="S57" t="n">
+        <v>13</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240002</t>
         </is>
       </c>
     </row>
@@ -1504,6 +6921,54 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137237179</v>
       </c>
       <c r="B3" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137237193</v>
       </c>
       <c r="B4" t="n">
-        <v>87611</v>
+        <v>87613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137240150</v>
       </c>
       <c r="B6" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>137237189</v>
       </c>
       <c r="B11" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>137239872</v>
       </c>
       <c r="B12" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>137239874</v>
       </c>
       <c r="B13" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>137239997</v>
       </c>
       <c r="B14" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>137239999</v>
       </c>
       <c r="B15" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>137240009</v>
       </c>
       <c r="B16" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>137237180</v>
       </c>
       <c r="B17" t="n">
-        <v>91924</v>
+        <v>91926</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>137237259</v>
       </c>
       <c r="B18" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>137237191</v>
       </c>
       <c r="B19" t="n">
-        <v>91576</v>
+        <v>91578</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>137237258</v>
       </c>
       <c r="B20" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>137239866</v>
       </c>
       <c r="B21" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>137239867</v>
       </c>
       <c r="B22" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>137239864</v>
       </c>
       <c r="B23" t="n">
-        <v>91537</v>
+        <v>91539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>137239869</v>
       </c>
       <c r="B24" t="n">
-        <v>91537</v>
+        <v>91539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>137239994</v>
       </c>
       <c r="B25" t="n">
-        <v>91537</v>
+        <v>91539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>137240171</v>
       </c>
       <c r="B26" t="n">
-        <v>91537</v>
+        <v>91539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>137239865</v>
       </c>
       <c r="B28" t="n">
-        <v>91544</v>
+        <v>91546</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>137239876</v>
       </c>
       <c r="B29" t="n">
-        <v>91544</v>
+        <v>91546</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>137239996</v>
       </c>
       <c r="B30" t="n">
-        <v>91544</v>
+        <v>91546</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>137237185</v>
       </c>
       <c r="B31" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>137239879</v>
       </c>
       <c r="B32" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>137240010</v>
       </c>
       <c r="B33" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>137237186</v>
       </c>
       <c r="B34" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>137239882</v>
       </c>
       <c r="B35" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>137237181</v>
       </c>
       <c r="B36" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>137237182</v>
       </c>
       <c r="B37" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>137237188</v>
       </c>
       <c r="B38" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>137237257</v>
       </c>
       <c r="B39" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>137237176</v>
       </c>
       <c r="B40" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>137240154</v>
       </c>
       <c r="B41" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>137237178</v>
       </c>
       <c r="B42" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>137237190</v>
       </c>
       <c r="B43" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>137237260</v>
       </c>
       <c r="B44" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>137237261</v>
       </c>
       <c r="B45" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>137237262</v>
       </c>
       <c r="B46" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>137239881</v>
       </c>
       <c r="B47" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>137240151</v>
       </c>
       <c r="B48" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>137240152</v>
       </c>
       <c r="B49" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>137240153</v>
       </c>
       <c r="B50" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>137240155</v>
       </c>
       <c r="B52" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>137239870</v>
       </c>
       <c r="B53" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>137239995</v>
       </c>
       <c r="B54" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>137240000</v>
       </c>
       <c r="B55" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>137239871</v>
       </c>
       <c r="B56" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>137240002</v>
       </c>
       <c r="B57" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ57"/>
+  <dimension ref="A1:AZ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96844888</v>
+        <v>137241048</v>
       </c>
       <c r="B5" t="n">
-        <v>87368</v>
+        <v>87616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,37 +1013,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720195</v>
+        <v>720174</v>
       </c>
       <c r="R5" t="n">
-        <v>6418206</v>
+        <v>6418179</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,12 +1063,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gran, en, mossa</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,49 +1098,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844888</t>
+          <t>https://artportalen.se/Sighting/137241048</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137240150</v>
+        <v>137241042</v>
       </c>
       <c r="B6" t="n">
-        <v>87499</v>
+        <v>87446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720064</v>
+        <v>720047</v>
       </c>
       <c r="R6" t="n">
-        <v>6418169</v>
+        <v>6418182</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1174,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1184,7 +1195,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hassel, gran, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,27 +1215,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240150</t>
+          <t>https://artportalen.se/Sighting/137241042</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96844938</v>
+        <v>96844888</v>
       </c>
       <c r="B7" t="n">
-        <v>79837</v>
+        <v>87368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1026</v>
+        <v>449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720087</v>
+        <v>720195</v>
       </c>
       <c r="R7" t="n">
-        <v>6418153</v>
+        <v>6418206</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,54 +1328,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844938</t>
+          <t>https://artportalen.se/Sighting/96844888</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96844939</v>
+        <v>137240150</v>
       </c>
       <c r="B8" t="n">
-        <v>79837</v>
+        <v>87499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1026</v>
+        <v>473</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720102</v>
+        <v>720064</v>
       </c>
       <c r="R8" t="n">
-        <v>6418150</v>
+        <v>6418169</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1383,12 +1399,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,49 +1429,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844939</t>
+          <t>https://artportalen.se/Sighting/137240150</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96844866</v>
+        <v>96844938</v>
       </c>
       <c r="B9" t="n">
-        <v>75336</v>
+        <v>79837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1116</v>
+        <v>1026</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720093</v>
+        <v>720087</v>
       </c>
       <c r="R9" t="n">
-        <v>6418136</v>
+        <v>6418153</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1516,38 +1542,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844866</t>
+          <t>https://artportalen.se/Sighting/96844938</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96844921</v>
+        <v>96844939</v>
       </c>
       <c r="B10" t="n">
-        <v>90663</v>
+        <v>79837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1595</v>
+        <v>1026</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720190</v>
+        <v>720102</v>
       </c>
       <c r="R10" t="n">
-        <v>6418114</v>
+        <v>6418150</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1618,54 +1644,54 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844921</t>
+          <t>https://artportalen.se/Sighting/96844939</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137237189</v>
+        <v>96844866</v>
       </c>
       <c r="B11" t="n">
-        <v>90880</v>
+        <v>75336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1595</v>
+        <v>1116</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Olarve Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720160</v>
+        <v>720093</v>
       </c>
       <c r="R11" t="n">
-        <v>6418175</v>
+        <v>6418136</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1689,22 +1715,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,27 +1735,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237189</t>
+          <t>https://artportalen.se/Sighting/96844866</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137239872</v>
+        <v>96844921</v>
       </c>
       <c r="B12" t="n">
-        <v>90880</v>
+        <v>90663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,17 +1783,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Olarve Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720183</v>
+        <v>720190</v>
       </c>
       <c r="R12" t="n">
-        <v>6418166</v>
+        <v>6418114</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1801,22 +1817,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,24 +1837,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239872</t>
+          <t>https://artportalen.se/Sighting/96844921</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137239874</v>
+        <v>137237189</v>
       </c>
       <c r="B13" t="n">
         <v>90880</v>
@@ -1883,13 +1889,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720205</v>
+        <v>720160</v>
       </c>
       <c r="R13" t="n">
-        <v>6418184</v>
+        <v>6418175</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1918,7 +1924,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1928,7 +1934,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1943,24 +1949,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239874</t>
+          <t>https://artportalen.se/Sighting/137237189</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137239997</v>
+        <v>137239872</v>
       </c>
       <c r="B14" t="n">
         <v>90880</v>
@@ -1988,29 +1994,20 @@
           <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720171</v>
+        <v>720183</v>
       </c>
       <c r="R14" t="n">
-        <v>6418150</v>
+        <v>6418166</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2036,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2046,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,24 +2061,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239997</t>
+          <t>https://artportalen.se/Sighting/137239872</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137239999</v>
+        <v>137239874</v>
       </c>
       <c r="B15" t="n">
         <v>90880</v>
@@ -2109,29 +2106,20 @@
           <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720200</v>
+        <v>720205</v>
       </c>
       <c r="R15" t="n">
-        <v>6418166</v>
+        <v>6418184</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2160,7 +2148,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2170,7 +2158,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2185,24 +2173,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239999</t>
+          <t>https://artportalen.se/Sighting/137239874</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137240009</v>
+        <v>137239997</v>
       </c>
       <c r="B16" t="n">
         <v>90880</v>
@@ -2232,7 +2220,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2246,13 +2234,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720160</v>
+        <v>720171</v>
       </c>
       <c r="R16" t="n">
-        <v>6418179</v>
+        <v>6418150</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,7 +2269,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2291,7 +2279,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,51 +2305,60 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240009</t>
+          <t>https://artportalen.se/Sighting/137239997</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137237180</v>
+        <v>137239999</v>
       </c>
       <c r="B17" t="n">
-        <v>91926</v>
+        <v>90880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2015</v>
+        <v>1595</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Peck</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720071</v>
+        <v>720200</v>
       </c>
       <c r="R17" t="n">
-        <v>6418186</v>
+        <v>6418166</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2393,7 +2390,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2403,7 +2400,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2418,27 +2415,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237180</t>
+          <t>https://artportalen.se/Sighting/137239999</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137237259</v>
+        <v>137240009</v>
       </c>
       <c r="B18" t="n">
-        <v>96603</v>
+        <v>90880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,37 +2443,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2812</v>
+        <v>1595</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720125</v>
+        <v>720160</v>
       </c>
       <c r="R18" t="n">
-        <v>6418174</v>
+        <v>6418179</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2505,7 +2511,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2515,7 +2521,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,49 +2536,49 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237259</t>
+          <t>https://artportalen.se/Sighting/137240009</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137237191</v>
+        <v>137237180</v>
       </c>
       <c r="B19" t="n">
-        <v>91578</v>
+        <v>91926</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3286</v>
+        <v>2015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2582,10 +2588,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720160</v>
+        <v>720071</v>
       </c>
       <c r="R19" t="n">
-        <v>6418178</v>
+        <v>6418186</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2617,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2627,7 +2633,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2653,16 +2659,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237191</t>
+          <t>https://artportalen.se/Sighting/137237180</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137237258</v>
+        <v>137237259</v>
       </c>
       <c r="B20" t="n">
-        <v>87519</v>
+        <v>96603</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2670,21 +2676,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3674</v>
+        <v>2812</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2694,13 +2700,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720154</v>
+        <v>720125</v>
       </c>
       <c r="R20" t="n">
-        <v>6418199</v>
+        <v>6418174</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2729,7 +2735,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2739,7 +2745,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,16 +2771,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237258</t>
+          <t>https://artportalen.se/Sighting/137237259</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137239866</v>
+        <v>137237191</v>
       </c>
       <c r="B21" t="n">
-        <v>87380</v>
+        <v>91578</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3712</v>
+        <v>3286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2806,13 +2812,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720051</v>
+        <v>720160</v>
       </c>
       <c r="R21" t="n">
-        <v>6418177</v>
+        <v>6418178</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2841,7 +2847,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2851,7 +2857,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2866,49 +2872,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239866</t>
+          <t>https://artportalen.se/Sighting/137237191</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137239867</v>
+        <v>137237258</v>
       </c>
       <c r="B22" t="n">
-        <v>87380</v>
+        <v>87519</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2918,13 +2924,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720120</v>
+        <v>720154</v>
       </c>
       <c r="R22" t="n">
-        <v>6418133</v>
+        <v>6418199</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2953,7 +2959,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2963,7 +2969,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2978,27 +2984,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239867</t>
+          <t>https://artportalen.se/Sighting/137237258</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137239864</v>
+        <v>137241043</v>
       </c>
       <c r="B23" t="n">
-        <v>91539</v>
+        <v>87522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,21 +3012,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4188</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3030,10 +3036,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720048</v>
+        <v>720069</v>
       </c>
       <c r="R23" t="n">
-        <v>6418177</v>
+        <v>6418169</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3065,7 +3071,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3075,7 +3081,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Tall, björk, en, ,hassel, gräs</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,27 +3101,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239864</t>
+          <t>https://artportalen.se/Sighting/137241043</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137239869</v>
+        <v>137273929</v>
       </c>
       <c r="B24" t="n">
-        <v>91539</v>
+        <v>87522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3118,21 +3129,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4188</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3142,13 +3153,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720155</v>
+        <v>720067</v>
       </c>
       <c r="R24" t="n">
-        <v>6418130</v>
+        <v>6418157</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3177,7 +3188,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3187,7 +3198,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3202,27 +3213,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239869</t>
+          <t>https://artportalen.se/Sighting/137273929</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137239994</v>
+        <v>137273932</v>
       </c>
       <c r="B25" t="n">
-        <v>91539</v>
+        <v>87522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3230,41 +3241,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4188</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720135</v>
+        <v>720142</v>
       </c>
       <c r="R25" t="n">
-        <v>6418121</v>
+        <v>6418180</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3293,7 +3300,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3303,7 +3310,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3318,49 +3325,49 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239994</t>
+          <t>https://artportalen.se/Sighting/137273932</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137240171</v>
+        <v>137239866</v>
       </c>
       <c r="B26" t="n">
-        <v>91539</v>
+        <v>87380</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4188</v>
+        <v>3712</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3370,13 +3377,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720159</v>
+        <v>720051</v>
       </c>
       <c r="R26" t="n">
-        <v>6418114</v>
+        <v>6418177</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3412,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3422,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3430,65 +3437,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240171</t>
+          <t>https://artportalen.se/Sighting/137239866</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96844877</v>
+        <v>137239867</v>
       </c>
       <c r="B27" t="n">
-        <v>91329</v>
+        <v>87380</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4191</v>
+        <v>3712</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720205</v>
+        <v>720120</v>
       </c>
       <c r="R27" t="n">
-        <v>6418151</v>
+        <v>6418133</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,12 +3519,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3532,49 +3549,49 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844877</t>
+          <t>https://artportalen.se/Sighting/137239867</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137239865</v>
+        <v>137241047</v>
       </c>
       <c r="B28" t="n">
-        <v>91546</v>
+        <v>87383</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4191</v>
+        <v>3712</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,13 +3601,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720051</v>
+        <v>720160</v>
       </c>
       <c r="R28" t="n">
-        <v>6418177</v>
+        <v>6418150</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3619,7 +3636,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,7 +3646,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gran, tall, mossa</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3638,55 +3660,56 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239865</t>
+          <t>https://artportalen.se/Sighting/137241047</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137239876</v>
+        <v>137273927</v>
       </c>
       <c r="B29" t="n">
-        <v>91546</v>
+        <v>87383</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4191</v>
+        <v>3712</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3696,13 +3719,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720202</v>
+        <v>720045</v>
       </c>
       <c r="R29" t="n">
-        <v>6418171</v>
+        <v>6418175</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3731,7 +3754,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,7 +3764,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3750,75 +3773,72 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239876</t>
+          <t>https://artportalen.se/Sighting/137273927</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137239996</v>
+        <v>137273931</v>
       </c>
       <c r="B30" t="n">
-        <v>91546</v>
+        <v>87383</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4191</v>
+        <v>3712</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720183</v>
+        <v>720113</v>
       </c>
       <c r="R30" t="n">
-        <v>6418149</v>
+        <v>6418129</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3847,7 +3867,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3857,7 +3877,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3866,55 +3886,56 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239996</t>
+          <t>https://artportalen.se/Sighting/137273931</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137237185</v>
+        <v>137239864</v>
       </c>
       <c r="B31" t="n">
-        <v>93436</v>
+        <v>91539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4188</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3924,13 +3945,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720136</v>
+        <v>720048</v>
       </c>
       <c r="R31" t="n">
-        <v>6418135</v>
+        <v>6418177</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3959,7 +3980,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3969,7 +3990,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3984,49 +4005,49 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237185</t>
+          <t>https://artportalen.se/Sighting/137239864</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137239879</v>
+        <v>137239869</v>
       </c>
       <c r="B32" t="n">
-        <v>93436</v>
+        <v>91539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>4188</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4036,13 +4057,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720201</v>
+        <v>720155</v>
       </c>
       <c r="R32" t="n">
-        <v>6418193</v>
+        <v>6418130</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4071,7 +4092,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4081,12 +4102,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Stor halvcirkel i löv/barrmatta under gran och hassel</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4112,54 +4128,58 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239879</t>
+          <t>https://artportalen.se/Sighting/137239869</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137240010</v>
+        <v>137239994</v>
       </c>
       <c r="B33" t="n">
-        <v>93478</v>
+        <v>91539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>4188</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720148</v>
+        <v>720135</v>
       </c>
       <c r="R33" t="n">
-        <v>6418164</v>
+        <v>6418121</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4188,7 +4208,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4198,7 +4218,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,38 +4244,38 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240010</t>
+          <t>https://artportalen.se/Sighting/137239994</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137237186</v>
+        <v>137240171</v>
       </c>
       <c r="B34" t="n">
-        <v>111689</v>
+        <v>91539</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219711</v>
+        <v>4188</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4265,10 +4285,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720139</v>
+        <v>720159</v>
       </c>
       <c r="R34" t="n">
-        <v>6418142</v>
+        <v>6418114</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4300,7 +4320,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4310,7 +4330,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4325,27 +4345,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237186</t>
+          <t>https://artportalen.se/Sighting/137240171</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137239882</v>
+        <v>137241045</v>
       </c>
       <c r="B35" t="n">
-        <v>99414</v>
+        <v>91542</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,21 +4373,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219862</v>
+        <v>4188</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4377,13 +4397,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720063</v>
+        <v>720130</v>
       </c>
       <c r="R35" t="n">
-        <v>6418152</v>
+        <v>6418145</v>
       </c>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4412,7 +4432,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4422,7 +4442,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4437,65 +4462,65 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239882</t>
+          <t>https://artportalen.se/Sighting/137241045</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137237181</v>
+        <v>96844877</v>
       </c>
       <c r="B36" t="n">
-        <v>102517</v>
+        <v>91329</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221235</v>
+        <v>4191</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Olarve Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720131</v>
+        <v>720205</v>
       </c>
       <c r="R36" t="n">
-        <v>6418123</v>
+        <v>6418151</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4519,22 +4544,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4549,49 +4564,49 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237181</t>
+          <t>https://artportalen.se/Sighting/96844877</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137237182</v>
+        <v>137239865</v>
       </c>
       <c r="B37" t="n">
-        <v>102517</v>
+        <v>91546</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221235</v>
+        <v>4191</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4601,13 +4616,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720151</v>
+        <v>720051</v>
       </c>
       <c r="R37" t="n">
-        <v>6418130</v>
+        <v>6418177</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4636,7 +4651,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4646,7 +4661,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4661,49 +4676,49 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237182</t>
+          <t>https://artportalen.se/Sighting/137239865</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137237188</v>
+        <v>137239876</v>
       </c>
       <c r="B38" t="n">
-        <v>102517</v>
+        <v>91546</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221235</v>
+        <v>4191</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4713,13 +4728,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720138</v>
+        <v>720202</v>
       </c>
       <c r="R38" t="n">
-        <v>6418145</v>
+        <v>6418171</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4748,7 +4763,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4758,7 +4773,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4773,65 +4788,69 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237188</t>
+          <t>https://artportalen.se/Sighting/137239876</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137237257</v>
+        <v>137239996</v>
       </c>
       <c r="B39" t="n">
-        <v>102517</v>
+        <v>91546</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221235</v>
+        <v>4191</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720127</v>
+        <v>720183</v>
       </c>
       <c r="R39" t="n">
-        <v>6418141</v>
+        <v>6418149</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4860,7 +4879,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4870,7 +4889,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4885,49 +4904,49 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237257</t>
+          <t>https://artportalen.se/Sighting/137239996</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137237176</v>
+        <v>137237185</v>
       </c>
       <c r="B40" t="n">
-        <v>87579</v>
+        <v>93436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>248947</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4937,13 +4956,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720035</v>
+        <v>720136</v>
       </c>
       <c r="R40" t="n">
-        <v>6418184</v>
+        <v>6418135</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4972,7 +4991,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4982,7 +5001,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5008,38 +5027,38 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237176</t>
+          <t>https://artportalen.se/Sighting/137237185</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137240154</v>
+        <v>137239879</v>
       </c>
       <c r="B41" t="n">
-        <v>87579</v>
+        <v>93436</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>248947</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5049,10 +5068,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720138</v>
+        <v>720201</v>
       </c>
       <c r="R41" t="n">
-        <v>6418133</v>
+        <v>6418193</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5084,7 +5103,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5094,7 +5113,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Stor halvcirkel i löv/barrmatta under gran och hassel</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5109,65 +5133,68 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240154</t>
+          <t>https://artportalen.se/Sighting/137239879</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137237178</v>
+        <v>137273938</v>
       </c>
       <c r="B42" t="n">
-        <v>87472</v>
+        <v>93439</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>248956</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720052</v>
+        <v>720169</v>
       </c>
       <c r="R42" t="n">
-        <v>6418183</v>
+        <v>6418107</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5196,7 +5223,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5206,7 +5233,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5215,55 +5242,56 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Margaret Rainey, Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237178</t>
+          <t>https://artportalen.se/Sighting/137273938</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137237190</v>
+        <v>137241044</v>
       </c>
       <c r="B43" t="n">
-        <v>87472</v>
+        <v>93457</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>248956</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5273,10 +5301,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720160</v>
+        <v>720127</v>
       </c>
       <c r="R43" t="n">
-        <v>6418176</v>
+        <v>6418124</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5308,7 +5336,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5318,7 +5346,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gran, en, mossa</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,49 +5366,49 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237190</t>
+          <t>https://artportalen.se/Sighting/137241044</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137237260</v>
+        <v>137240010</v>
       </c>
       <c r="B44" t="n">
-        <v>87472</v>
+        <v>93478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>248956</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5385,13 +5418,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720065</v>
+        <v>720148</v>
       </c>
       <c r="R44" t="n">
-        <v>6418154</v>
+        <v>6418164</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5420,7 +5453,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5430,7 +5463,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5445,49 +5478,49 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237260</t>
+          <t>https://artportalen.se/Sighting/137240010</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137237261</v>
+        <v>137241046</v>
       </c>
       <c r="B45" t="n">
-        <v>87472</v>
+        <v>93481</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>248956</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5497,13 +5530,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720051</v>
+        <v>720148</v>
       </c>
       <c r="R45" t="n">
-        <v>6418162</v>
+        <v>6418161</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5532,7 +5565,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5542,7 +5575,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Gran, en, mossa</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5557,49 +5595,49 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237261</t>
+          <t>https://artportalen.se/Sighting/137241046</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137237262</v>
+        <v>137237186</v>
       </c>
       <c r="B46" t="n">
-        <v>87472</v>
+        <v>111689</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>248956</v>
+        <v>219711</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5609,13 +5647,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720034</v>
+        <v>720139</v>
       </c>
       <c r="R46" t="n">
-        <v>6418163</v>
+        <v>6418142</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5644,7 +5682,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5654,7 +5692,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5680,38 +5718,38 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237262</t>
+          <t>https://artportalen.se/Sighting/137237186</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137239881</v>
+        <v>137239882</v>
       </c>
       <c r="B47" t="n">
-        <v>87472</v>
+        <v>99414</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>248956</v>
+        <v>219862</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5721,13 +5759,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720152</v>
+        <v>720063</v>
       </c>
       <c r="R47" t="n">
-        <v>6418189</v>
+        <v>6418152</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5756,7 +5794,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5766,7 +5804,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5792,38 +5830,38 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239881</t>
+          <t>https://artportalen.se/Sighting/137239882</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137240151</v>
+        <v>137237181</v>
       </c>
       <c r="B48" t="n">
-        <v>87472</v>
+        <v>102517</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>248956</v>
+        <v>221235</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5833,13 +5871,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720062</v>
+        <v>720131</v>
       </c>
       <c r="R48" t="n">
-        <v>6418146</v>
+        <v>6418123</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5893,49 +5931,49 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240151</t>
+          <t>https://artportalen.se/Sighting/137237181</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137240152</v>
+        <v>137237182</v>
       </c>
       <c r="B49" t="n">
-        <v>87472</v>
+        <v>102517</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>248956</v>
+        <v>221235</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5945,13 +5983,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>720059</v>
+        <v>720151</v>
       </c>
       <c r="R49" t="n">
-        <v>6418149</v>
+        <v>6418130</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5980,7 +6018,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5990,7 +6028,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6005,49 +6043,49 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240152</t>
+          <t>https://artportalen.se/Sighting/137237182</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137240153</v>
+        <v>137237188</v>
       </c>
       <c r="B50" t="n">
-        <v>87472</v>
+        <v>102517</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>248956</v>
+        <v>221235</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6057,13 +6095,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720059</v>
+        <v>720138</v>
       </c>
       <c r="R50" t="n">
-        <v>6418142</v>
+        <v>6418145</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6092,7 +6130,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6102,7 +6140,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6117,27 +6155,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240153</t>
+          <t>https://artportalen.se/Sighting/137237188</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>96844899</v>
+        <v>137237257</v>
       </c>
       <c r="B51" t="n">
-        <v>87346</v>
+        <v>102517</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,37 +6183,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6003295</v>
+        <v>221235</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>720160</v>
+        <v>720127</v>
       </c>
       <c r="R51" t="n">
-        <v>6418181</v>
+        <v>6418141</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6199,12 +6237,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6219,49 +6267,49 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844899</t>
+          <t>https://artportalen.se/Sighting/137237257</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137240155</v>
+        <v>137237176</v>
       </c>
       <c r="B52" t="n">
-        <v>87556</v>
+        <v>87579</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6271,10 +6319,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>720146</v>
+        <v>720035</v>
       </c>
       <c r="R52" t="n">
-        <v>6418153</v>
+        <v>6418184</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6306,7 +6354,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6316,7 +6364,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6325,54 +6373,57 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240155</t>
+          <t>https://artportalen.se/Sighting/137237176</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137239870</v>
+        <v>137240154</v>
       </c>
       <c r="B53" t="n">
-        <v>93456</v>
+        <v>87579</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6047725</v>
+        <v>248947</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6380,13 +6431,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>720172</v>
+        <v>720138</v>
       </c>
       <c r="R53" t="n">
-        <v>6418159</v>
+        <v>6418133</v>
       </c>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6415,7 +6466,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6425,7 +6476,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6440,47 +6491,51 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239870</t>
+          <t>https://artportalen.se/Sighting/137240154</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137239995</v>
+        <v>137237178</v>
       </c>
       <c r="B54" t="n">
-        <v>93456</v>
+        <v>87472</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6047725</v>
+        <v>248956</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6488,13 +6543,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>720134</v>
+        <v>720052</v>
       </c>
       <c r="R54" t="n">
-        <v>6418126</v>
+        <v>6418183</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6523,7 +6578,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6533,12 +6588,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ej skarp smak</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6553,64 +6603,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239995</t>
+          <t>https://artportalen.se/Sighting/137237178</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137240000</v>
+        <v>137237190</v>
       </c>
       <c r="B55" t="n">
-        <v>93456</v>
+        <v>87472</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6047725</v>
+        <v>248956</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>720174</v>
+        <v>720160</v>
       </c>
       <c r="R55" t="n">
-        <v>6418161</v>
+        <v>6418176</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6639,7 +6690,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6649,12 +6700,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ej skarp smak</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6663,56 +6709,55 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240000</t>
+          <t>https://artportalen.se/Sighting/137237190</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137239871</v>
+        <v>137237260</v>
       </c>
       <c r="B56" t="n">
-        <v>93470</v>
+        <v>87472</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6332770</v>
+        <v>248956</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6722,10 +6767,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>720191</v>
+        <v>720065</v>
       </c>
       <c r="R56" t="n">
-        <v>6418148</v>
+        <v>6418154</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6757,7 +6802,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6767,7 +6812,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6776,56 +6821,55 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239871</t>
+          <t>https://artportalen.se/Sighting/137237260</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137240002</v>
+        <v>137237261</v>
       </c>
       <c r="B57" t="n">
-        <v>93470</v>
+        <v>87472</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6332770</v>
+        <v>248956</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6835,13 +6879,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>720178</v>
+        <v>720051</v>
       </c>
       <c r="R57" t="n">
-        <v>6418157</v>
+        <v>6418162</v>
       </c>
       <c r="S57" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6870,7 +6914,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6880,7 +6924,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6889,23 +6933,1474 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237261</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137237262</v>
+      </c>
+      <c r="B58" t="n">
+        <v>87472</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>720034</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6418163</v>
+      </c>
+      <c r="S58" t="n">
+        <v>9</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237262</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>137239881</v>
+      </c>
+      <c r="B59" t="n">
+        <v>87472</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>720152</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6418189</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239881</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>137240151</v>
+      </c>
+      <c r="B60" t="n">
+        <v>87472</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>720062</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6418146</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240151</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>137240152</v>
+      </c>
+      <c r="B61" t="n">
+        <v>87472</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>720059</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6418149</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240152</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>137240153</v>
+      </c>
+      <c r="B62" t="n">
+        <v>87472</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>720059</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6418142</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240153</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>96844899</v>
+      </c>
+      <c r="B63" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>720160</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6418181</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844899</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>137240155</v>
+      </c>
+      <c r="B64" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>720146</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6418153</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240155</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>137273930</v>
+      </c>
+      <c r="B65" t="n">
+        <v>87559</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>720071</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6418150</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273930</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>137239870</v>
+      </c>
+      <c r="B66" t="n">
+        <v>93456</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>720172</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6418159</v>
+      </c>
+      <c r="S66" t="n">
+        <v>6</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239870</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>137239995</v>
+      </c>
+      <c r="B67" t="n">
+        <v>93456</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>720134</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6418126</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ej skarp smak</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239995</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>137240000</v>
+      </c>
+      <c r="B68" t="n">
+        <v>93456</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>720174</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6418161</v>
+      </c>
+      <c r="S68" t="n">
+        <v>6</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ej skarp smak</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240000</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>137239871</v>
+      </c>
+      <c r="B69" t="n">
+        <v>93470</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>720191</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6418148</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239871</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>137240002</v>
+      </c>
+      <c r="B70" t="n">
+        <v>93470</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>720178</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6418157</v>
+      </c>
+      <c r="S70" t="n">
+        <v>13</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137240002</t>
         </is>
@@ -6969,6 +8464,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137237179</v>
       </c>
       <c r="B3" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137237193</v>
       </c>
       <c r="B4" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>137240150</v>
       </c>
       <c r="B8" t="n">
-        <v>87499</v>
+        <v>87502</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137237189</v>
       </c>
       <c r="B13" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>137239872</v>
       </c>
       <c r="B14" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>137239874</v>
       </c>
       <c r="B15" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>137239997</v>
       </c>
       <c r="B16" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137239999</v>
       </c>
       <c r="B17" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137240009</v>
       </c>
       <c r="B18" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137237180</v>
       </c>
       <c r="B19" t="n">
-        <v>91926</v>
+        <v>91929</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137237259</v>
       </c>
       <c r="B20" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>137237191</v>
       </c>
       <c r="B21" t="n">
-        <v>91578</v>
+        <v>91581</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>137237258</v>
       </c>
       <c r="B22" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137239866</v>
       </c>
       <c r="B26" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137239867</v>
       </c>
       <c r="B27" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>137239864</v>
       </c>
       <c r="B31" t="n">
-        <v>91539</v>
+        <v>91542</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137239869</v>
       </c>
       <c r="B32" t="n">
-        <v>91539</v>
+        <v>91542</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>137239994</v>
       </c>
       <c r="B33" t="n">
-        <v>91539</v>
+        <v>91542</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>137240171</v>
       </c>
       <c r="B34" t="n">
-        <v>91539</v>
+        <v>91542</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>137239865</v>
       </c>
       <c r="B37" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>137239876</v>
       </c>
       <c r="B38" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>137239996</v>
       </c>
       <c r="B39" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>137237185</v>
       </c>
       <c r="B40" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>137239879</v>
       </c>
       <c r="B41" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>137240010</v>
       </c>
       <c r="B44" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137237186</v>
       </c>
       <c r="B46" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137239882</v>
       </c>
       <c r="B47" t="n">
-        <v>99414</v>
+        <v>99417</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137237181</v>
       </c>
       <c r="B48" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137237182</v>
       </c>
       <c r="B49" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137237188</v>
       </c>
       <c r="B50" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>137237257</v>
       </c>
       <c r="B51" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>137237176</v>
       </c>
       <c r="B52" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>137240154</v>
       </c>
       <c r="B53" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>137237178</v>
       </c>
       <c r="B54" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237190</v>
       </c>
       <c r="B55" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237260</v>
       </c>
       <c r="B56" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237261</v>
       </c>
       <c r="B57" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137237262</v>
       </c>
       <c r="B58" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137239881</v>
       </c>
       <c r="B59" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240151</v>
       </c>
       <c r="B60" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240152</v>
       </c>
       <c r="B61" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240153</v>
       </c>
       <c r="B62" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>137240155</v>
       </c>
       <c r="B64" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>137239870</v>
       </c>
       <c r="B66" t="n">
-        <v>93456</v>
+        <v>93459</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>137239995</v>
       </c>
       <c r="B67" t="n">
-        <v>93456</v>
+        <v>93459</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137240000</v>
       </c>
       <c r="B68" t="n">
-        <v>93456</v>
+        <v>93459</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137239871</v>
       </c>
       <c r="B69" t="n">
-        <v>93470</v>
+        <v>93473</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>137240002</v>
       </c>
       <c r="B70" t="n">
-        <v>93470</v>
+        <v>93473</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137237179</v>
       </c>
       <c r="B3" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137237193</v>
       </c>
       <c r="B4" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137241048</v>
       </c>
       <c r="B5" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>137241042</v>
       </c>
       <c r="B6" t="n">
-        <v>87446</v>
+        <v>87456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>137240150</v>
       </c>
       <c r="B8" t="n">
-        <v>87502</v>
+        <v>87512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137237189</v>
       </c>
       <c r="B13" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>137239872</v>
       </c>
       <c r="B14" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>137239874</v>
       </c>
       <c r="B15" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>137239997</v>
       </c>
       <c r="B16" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137239999</v>
       </c>
       <c r="B17" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137240009</v>
       </c>
       <c r="B18" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137237180</v>
       </c>
       <c r="B19" t="n">
-        <v>91929</v>
+        <v>91939</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137237259</v>
       </c>
       <c r="B20" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>137237191</v>
       </c>
       <c r="B21" t="n">
-        <v>91581</v>
+        <v>91591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>137237258</v>
       </c>
       <c r="B22" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>137241043</v>
       </c>
       <c r="B23" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>137273929</v>
       </c>
       <c r="B24" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>137273932</v>
       </c>
       <c r="B25" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137239866</v>
       </c>
       <c r="B26" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137239867</v>
       </c>
       <c r="B27" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>137241047</v>
       </c>
       <c r="B28" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>137273927</v>
       </c>
       <c r="B29" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>137273931</v>
       </c>
       <c r="B30" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>137239864</v>
       </c>
       <c r="B31" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137239869</v>
       </c>
       <c r="B32" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>137239994</v>
       </c>
       <c r="B33" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>137240171</v>
       </c>
       <c r="B34" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>137241045</v>
       </c>
       <c r="B35" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>137239865</v>
       </c>
       <c r="B37" t="n">
-        <v>91549</v>
+        <v>91559</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>137239876</v>
       </c>
       <c r="B38" t="n">
-        <v>91549</v>
+        <v>91559</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>137239996</v>
       </c>
       <c r="B39" t="n">
-        <v>91549</v>
+        <v>91559</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>137237185</v>
       </c>
       <c r="B40" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>137239879</v>
       </c>
       <c r="B41" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>137273938</v>
       </c>
       <c r="B42" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>137241044</v>
       </c>
       <c r="B43" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>137240010</v>
       </c>
       <c r="B44" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>137241046</v>
       </c>
       <c r="B45" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137237186</v>
       </c>
       <c r="B46" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137239882</v>
       </c>
       <c r="B47" t="n">
-        <v>99417</v>
+        <v>99427</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137237181</v>
       </c>
       <c r="B48" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137237182</v>
       </c>
       <c r="B49" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137237188</v>
       </c>
       <c r="B50" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>137237257</v>
       </c>
       <c r="B51" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>137237176</v>
       </c>
       <c r="B52" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>137240154</v>
       </c>
       <c r="B53" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>137237178</v>
       </c>
       <c r="B54" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237190</v>
       </c>
       <c r="B55" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237260</v>
       </c>
       <c r="B56" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237261</v>
       </c>
       <c r="B57" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137237262</v>
       </c>
       <c r="B58" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137239881</v>
       </c>
       <c r="B59" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240151</v>
       </c>
       <c r="B60" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240152</v>
       </c>
       <c r="B61" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240153</v>
       </c>
       <c r="B62" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>137240155</v>
       </c>
       <c r="B64" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>137273930</v>
       </c>
       <c r="B65" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>137239870</v>
       </c>
       <c r="B66" t="n">
-        <v>93459</v>
+        <v>93469</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>137239995</v>
       </c>
       <c r="B67" t="n">
-        <v>93459</v>
+        <v>93469</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137240000</v>
       </c>
       <c r="B68" t="n">
-        <v>93459</v>
+        <v>93469</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137239871</v>
       </c>
       <c r="B69" t="n">
-        <v>93473</v>
+        <v>93483</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>137240002</v>
       </c>
       <c r="B70" t="n">
-        <v>93473</v>
+        <v>93483</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137237179</v>
       </c>
       <c r="B3" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137237193</v>
       </c>
       <c r="B4" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137241048</v>
       </c>
       <c r="B5" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>137241042</v>
       </c>
       <c r="B6" t="n">
-        <v>87456</v>
+        <v>87457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>137240150</v>
       </c>
       <c r="B8" t="n">
-        <v>87512</v>
+        <v>87513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137237189</v>
       </c>
       <c r="B13" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>137239872</v>
       </c>
       <c r="B14" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>137239874</v>
       </c>
       <c r="B15" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>137239997</v>
       </c>
       <c r="B16" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137239999</v>
       </c>
       <c r="B17" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137240009</v>
       </c>
       <c r="B18" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137237180</v>
       </c>
       <c r="B19" t="n">
-        <v>91939</v>
+        <v>91940</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137237259</v>
       </c>
       <c r="B20" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>137237191</v>
       </c>
       <c r="B21" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>137237258</v>
       </c>
       <c r="B22" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>137241043</v>
       </c>
       <c r="B23" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>137273929</v>
       </c>
       <c r="B24" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>137273932</v>
       </c>
       <c r="B25" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137239866</v>
       </c>
       <c r="B26" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137239867</v>
       </c>
       <c r="B27" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>137241047</v>
       </c>
       <c r="B28" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>137273927</v>
       </c>
       <c r="B29" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>137273931</v>
       </c>
       <c r="B30" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>137239864</v>
       </c>
       <c r="B31" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137239869</v>
       </c>
       <c r="B32" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>137239994</v>
       </c>
       <c r="B33" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>137240171</v>
       </c>
       <c r="B34" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>137241045</v>
       </c>
       <c r="B35" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>137239865</v>
       </c>
       <c r="B37" t="n">
-        <v>91559</v>
+        <v>91560</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>137239876</v>
       </c>
       <c r="B38" t="n">
-        <v>91559</v>
+        <v>91560</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>137239996</v>
       </c>
       <c r="B39" t="n">
-        <v>91559</v>
+        <v>91560</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>137237185</v>
       </c>
       <c r="B40" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>137239879</v>
       </c>
       <c r="B41" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>137273938</v>
       </c>
       <c r="B42" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>137241044</v>
       </c>
       <c r="B43" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>137240010</v>
       </c>
       <c r="B44" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>137241046</v>
       </c>
       <c r="B45" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137237186</v>
       </c>
       <c r="B46" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137239882</v>
       </c>
       <c r="B47" t="n">
-        <v>99427</v>
+        <v>99428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137237181</v>
       </c>
       <c r="B48" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137237182</v>
       </c>
       <c r="B49" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137237188</v>
       </c>
       <c r="B50" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>137237257</v>
       </c>
       <c r="B51" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>137237176</v>
       </c>
       <c r="B52" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>137240154</v>
       </c>
       <c r="B53" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>137237178</v>
       </c>
       <c r="B54" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237190</v>
       </c>
       <c r="B55" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237260</v>
       </c>
       <c r="B56" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237261</v>
       </c>
       <c r="B57" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137237262</v>
       </c>
       <c r="B58" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137239881</v>
       </c>
       <c r="B59" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240151</v>
       </c>
       <c r="B60" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240152</v>
       </c>
       <c r="B61" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240153</v>
       </c>
       <c r="B62" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>137240155</v>
       </c>
       <c r="B64" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>137273930</v>
       </c>
       <c r="B65" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>137239870</v>
       </c>
       <c r="B66" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>137239995</v>
       </c>
       <c r="B67" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137240000</v>
       </c>
       <c r="B68" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137239871</v>
       </c>
       <c r="B69" t="n">
-        <v>93483</v>
+        <v>93484</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>137240002</v>
       </c>
       <c r="B70" t="n">
-        <v>93483</v>
+        <v>93484</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137237179</v>
       </c>
       <c r="B3" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137237193</v>
       </c>
       <c r="B4" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137241048</v>
       </c>
       <c r="B5" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>137241042</v>
       </c>
       <c r="B6" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>137240150</v>
       </c>
       <c r="B8" t="n">
-        <v>87513</v>
+        <v>87516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137237189</v>
       </c>
       <c r="B13" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>137239872</v>
       </c>
       <c r="B14" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>137239874</v>
       </c>
       <c r="B15" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>137239997</v>
       </c>
       <c r="B16" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137239999</v>
       </c>
       <c r="B17" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137240009</v>
       </c>
       <c r="B18" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137237180</v>
       </c>
       <c r="B19" t="n">
-        <v>91940</v>
+        <v>91943</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137237259</v>
       </c>
       <c r="B20" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>137237191</v>
       </c>
       <c r="B21" t="n">
-        <v>91592</v>
+        <v>91595</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>137237258</v>
       </c>
       <c r="B22" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>137241043</v>
       </c>
       <c r="B23" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>137273929</v>
       </c>
       <c r="B24" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>137273932</v>
       </c>
       <c r="B25" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137239866</v>
       </c>
       <c r="B26" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137239867</v>
       </c>
       <c r="B27" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>137241047</v>
       </c>
       <c r="B28" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>137273927</v>
       </c>
       <c r="B29" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>137273931</v>
       </c>
       <c r="B30" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>137239864</v>
       </c>
       <c r="B31" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137239869</v>
       </c>
       <c r="B32" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>137239994</v>
       </c>
       <c r="B33" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>137240171</v>
       </c>
       <c r="B34" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>137241045</v>
       </c>
       <c r="B35" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>137239865</v>
       </c>
       <c r="B37" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>137239876</v>
       </c>
       <c r="B38" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>137239996</v>
       </c>
       <c r="B39" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>137237185</v>
       </c>
       <c r="B40" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>137239879</v>
       </c>
       <c r="B41" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>137273938</v>
       </c>
       <c r="B42" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>137241044</v>
       </c>
       <c r="B43" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>137240010</v>
       </c>
       <c r="B44" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>137241046</v>
       </c>
       <c r="B45" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137237186</v>
       </c>
       <c r="B46" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137239882</v>
       </c>
       <c r="B47" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137237181</v>
       </c>
       <c r="B48" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137237182</v>
       </c>
       <c r="B49" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137237188</v>
       </c>
       <c r="B50" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>137237257</v>
       </c>
       <c r="B51" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>137237176</v>
       </c>
       <c r="B52" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>137240154</v>
       </c>
       <c r="B53" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>137237178</v>
       </c>
       <c r="B54" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237190</v>
       </c>
       <c r="B55" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237260</v>
       </c>
       <c r="B56" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237261</v>
       </c>
       <c r="B57" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137237262</v>
       </c>
       <c r="B58" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137239881</v>
       </c>
       <c r="B59" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240151</v>
       </c>
       <c r="B60" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240152</v>
       </c>
       <c r="B61" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240153</v>
       </c>
       <c r="B62" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>137240155</v>
       </c>
       <c r="B64" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>137273930</v>
       </c>
       <c r="B65" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>137239870</v>
       </c>
       <c r="B66" t="n">
-        <v>93470</v>
+        <v>93475</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>137239995</v>
       </c>
       <c r="B67" t="n">
-        <v>93470</v>
+        <v>93475</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137240000</v>
       </c>
       <c r="B68" t="n">
-        <v>93470</v>
+        <v>93475</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137239871</v>
       </c>
       <c r="B69" t="n">
-        <v>93484</v>
+        <v>93489</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>137240002</v>
       </c>
       <c r="B70" t="n">
-        <v>93484</v>
+        <v>93489</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -2556,7 +2556,7 @@
         <v>137237180</v>
       </c>
       <c r="B19" t="n">
-        <v>91943</v>
+        <v>91945</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137237259</v>
       </c>
       <c r="B20" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>137237191</v>
       </c>
       <c r="B21" t="n">
-        <v>91595</v>
+        <v>91597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>137239864</v>
       </c>
       <c r="B31" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137239869</v>
       </c>
       <c r="B32" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>137239994</v>
       </c>
       <c r="B33" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>137240171</v>
       </c>
       <c r="B34" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>137241045</v>
       </c>
       <c r="B35" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>137239865</v>
       </c>
       <c r="B37" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>137239876</v>
       </c>
       <c r="B38" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>137239996</v>
       </c>
       <c r="B39" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>137237185</v>
       </c>
       <c r="B40" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>137239879</v>
       </c>
       <c r="B41" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>137273938</v>
       </c>
       <c r="B42" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>137241044</v>
       </c>
       <c r="B43" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>137240010</v>
       </c>
       <c r="B44" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>137241046</v>
       </c>
       <c r="B45" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137237186</v>
       </c>
       <c r="B46" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137239882</v>
       </c>
       <c r="B47" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137237181</v>
       </c>
       <c r="B48" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137237182</v>
       </c>
       <c r="B49" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137237188</v>
       </c>
       <c r="B50" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>137237257</v>
       </c>
       <c r="B51" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>137239870</v>
       </c>
       <c r="B66" t="n">
-        <v>93475</v>
+        <v>93477</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>137239995</v>
       </c>
       <c r="B67" t="n">
-        <v>93475</v>
+        <v>93477</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137240000</v>
       </c>
       <c r="B68" t="n">
-        <v>93475</v>
+        <v>93477</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137239871</v>
       </c>
       <c r="B69" t="n">
-        <v>93489</v>
+        <v>93491</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>137240002</v>
       </c>
       <c r="B70" t="n">
-        <v>93489</v>
+        <v>93491</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137237179</v>
       </c>
       <c r="B3" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137237193</v>
       </c>
       <c r="B4" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137241048</v>
       </c>
       <c r="B5" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>137241042</v>
       </c>
       <c r="B6" t="n">
-        <v>87460</v>
+        <v>87465</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>137240150</v>
       </c>
       <c r="B8" t="n">
-        <v>87516</v>
+        <v>87521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137237189</v>
       </c>
       <c r="B13" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>137239872</v>
       </c>
       <c r="B14" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>137239874</v>
       </c>
       <c r="B15" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>137239997</v>
       </c>
       <c r="B16" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137239999</v>
       </c>
       <c r="B17" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137240009</v>
       </c>
       <c r="B18" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137237180</v>
       </c>
       <c r="B19" t="n">
-        <v>91945</v>
+        <v>91950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137237259</v>
       </c>
       <c r="B20" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>137237191</v>
       </c>
       <c r="B21" t="n">
-        <v>91597</v>
+        <v>91602</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>137237258</v>
       </c>
       <c r="B22" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>137241043</v>
       </c>
       <c r="B23" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>137273929</v>
       </c>
       <c r="B24" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>137273932</v>
       </c>
       <c r="B25" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137239866</v>
       </c>
       <c r="B26" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137239867</v>
       </c>
       <c r="B27" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>137241047</v>
       </c>
       <c r="B28" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>137273927</v>
       </c>
       <c r="B29" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>137273931</v>
       </c>
       <c r="B30" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>137239864</v>
       </c>
       <c r="B31" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137239869</v>
       </c>
       <c r="B32" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>137239994</v>
       </c>
       <c r="B33" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>137240171</v>
       </c>
       <c r="B34" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>137241045</v>
       </c>
       <c r="B35" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>137239865</v>
       </c>
       <c r="B37" t="n">
-        <v>91565</v>
+        <v>91570</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>137239876</v>
       </c>
       <c r="B38" t="n">
-        <v>91565</v>
+        <v>91570</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>137239996</v>
       </c>
       <c r="B39" t="n">
-        <v>91565</v>
+        <v>91570</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>137237185</v>
       </c>
       <c r="B40" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>137239879</v>
       </c>
       <c r="B41" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>137273938</v>
       </c>
       <c r="B42" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>137241044</v>
       </c>
       <c r="B43" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>137240010</v>
       </c>
       <c r="B44" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>137241046</v>
       </c>
       <c r="B45" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137237186</v>
       </c>
       <c r="B46" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137239882</v>
       </c>
       <c r="B47" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137237181</v>
       </c>
       <c r="B48" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137237182</v>
       </c>
       <c r="B49" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137237188</v>
       </c>
       <c r="B50" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>137237257</v>
       </c>
       <c r="B51" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>137237176</v>
       </c>
       <c r="B52" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>137240154</v>
       </c>
       <c r="B53" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>137237178</v>
       </c>
       <c r="B54" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237190</v>
       </c>
       <c r="B55" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237260</v>
       </c>
       <c r="B56" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237261</v>
       </c>
       <c r="B57" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137237262</v>
       </c>
       <c r="B58" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137239881</v>
       </c>
       <c r="B59" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240151</v>
       </c>
       <c r="B60" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240152</v>
       </c>
       <c r="B61" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240153</v>
       </c>
       <c r="B62" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>137240155</v>
       </c>
       <c r="B64" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>137273930</v>
       </c>
       <c r="B65" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>137239870</v>
       </c>
       <c r="B66" t="n">
-        <v>93477</v>
+        <v>93483</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>137239995</v>
       </c>
       <c r="B67" t="n">
-        <v>93477</v>
+        <v>93483</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137240000</v>
       </c>
       <c r="B68" t="n">
-        <v>93477</v>
+        <v>93483</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137239871</v>
       </c>
       <c r="B69" t="n">
-        <v>93491</v>
+        <v>93497</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>137240002</v>
       </c>
       <c r="B70" t="n">
-        <v>93491</v>
+        <v>93497</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -5615,7 +5615,7 @@
         <v>137237186</v>
       </c>
       <c r="B46" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137237179</v>
       </c>
       <c r="B3" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137237193</v>
       </c>
       <c r="B4" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137241048</v>
       </c>
       <c r="B5" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>137241042</v>
       </c>
       <c r="B6" t="n">
-        <v>87465</v>
+        <v>87476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>137240150</v>
       </c>
       <c r="B8" t="n">
-        <v>87521</v>
+        <v>87532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137237189</v>
       </c>
       <c r="B13" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>137239872</v>
       </c>
       <c r="B14" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>137239874</v>
       </c>
       <c r="B15" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>137239997</v>
       </c>
       <c r="B16" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137239999</v>
       </c>
       <c r="B17" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137240009</v>
       </c>
       <c r="B18" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137237180</v>
       </c>
       <c r="B19" t="n">
-        <v>91950</v>
+        <v>91962</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137237259</v>
       </c>
       <c r="B20" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>137237191</v>
       </c>
       <c r="B21" t="n">
-        <v>91602</v>
+        <v>91614</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>137237258</v>
       </c>
       <c r="B22" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>137241043</v>
       </c>
       <c r="B23" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>137273929</v>
       </c>
       <c r="B24" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>137273932</v>
       </c>
       <c r="B25" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137239866</v>
       </c>
       <c r="B26" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137239867</v>
       </c>
       <c r="B27" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>137241047</v>
       </c>
       <c r="B28" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>137273927</v>
       </c>
       <c r="B29" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>137273931</v>
       </c>
       <c r="B30" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>137239864</v>
       </c>
       <c r="B31" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137239869</v>
       </c>
       <c r="B32" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>137239994</v>
       </c>
       <c r="B33" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>137240171</v>
       </c>
       <c r="B34" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>137241045</v>
       </c>
       <c r="B35" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>137239865</v>
       </c>
       <c r="B37" t="n">
-        <v>91570</v>
+        <v>91582</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>137239876</v>
       </c>
       <c r="B38" t="n">
-        <v>91570</v>
+        <v>91582</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>137239996</v>
       </c>
       <c r="B39" t="n">
-        <v>91570</v>
+        <v>91582</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>137237185</v>
       </c>
       <c r="B40" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>137239879</v>
       </c>
       <c r="B41" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>137273938</v>
       </c>
       <c r="B42" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>137241044</v>
       </c>
       <c r="B43" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>137240010</v>
       </c>
       <c r="B44" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>137241046</v>
       </c>
       <c r="B45" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137237186</v>
       </c>
       <c r="B46" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137239882</v>
       </c>
       <c r="B47" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137237181</v>
       </c>
       <c r="B48" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137237182</v>
       </c>
       <c r="B49" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137237188</v>
       </c>
       <c r="B50" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>137237257</v>
       </c>
       <c r="B51" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>137237176</v>
       </c>
       <c r="B52" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>137240154</v>
       </c>
       <c r="B53" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>137237178</v>
       </c>
       <c r="B54" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237190</v>
       </c>
       <c r="B55" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237260</v>
       </c>
       <c r="B56" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237261</v>
       </c>
       <c r="B57" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137237262</v>
       </c>
       <c r="B58" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137239881</v>
       </c>
       <c r="B59" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240151</v>
       </c>
       <c r="B60" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240152</v>
       </c>
       <c r="B61" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240153</v>
       </c>
       <c r="B62" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>137240155</v>
       </c>
       <c r="B64" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>137273930</v>
       </c>
       <c r="B65" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>137239870</v>
       </c>
       <c r="B66" t="n">
-        <v>93483</v>
+        <v>93495</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>137239995</v>
       </c>
       <c r="B67" t="n">
-        <v>93483</v>
+        <v>93495</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137240000</v>
       </c>
       <c r="B68" t="n">
-        <v>93483</v>
+        <v>93495</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137239871</v>
       </c>
       <c r="B69" t="n">
-        <v>93497</v>
+        <v>93509</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>137240002</v>
       </c>
       <c r="B70" t="n">
-        <v>93497</v>
+        <v>93509</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137237179</v>
       </c>
       <c r="B3" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137237193</v>
       </c>
       <c r="B4" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137241048</v>
       </c>
       <c r="B5" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>137241042</v>
       </c>
       <c r="B6" t="n">
-        <v>87476</v>
+        <v>87477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>137240150</v>
       </c>
       <c r="B8" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137237189</v>
       </c>
       <c r="B13" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>137239872</v>
       </c>
       <c r="B14" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>137239874</v>
       </c>
       <c r="B15" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>137239997</v>
       </c>
       <c r="B16" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137239999</v>
       </c>
       <c r="B17" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137240009</v>
       </c>
       <c r="B18" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137237180</v>
       </c>
       <c r="B19" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137237259</v>
       </c>
       <c r="B20" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>137237191</v>
       </c>
       <c r="B21" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>137237258</v>
       </c>
       <c r="B22" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>137241043</v>
       </c>
       <c r="B23" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>137273929</v>
       </c>
       <c r="B24" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>137273932</v>
       </c>
       <c r="B25" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137239866</v>
       </c>
       <c r="B26" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137239867</v>
       </c>
       <c r="B27" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>137241047</v>
       </c>
       <c r="B28" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>137273927</v>
       </c>
       <c r="B29" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>137273931</v>
       </c>
       <c r="B30" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>137239864</v>
       </c>
       <c r="B31" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137239869</v>
       </c>
       <c r="B32" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>137239994</v>
       </c>
       <c r="B33" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>137240171</v>
       </c>
       <c r="B34" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>137241045</v>
       </c>
       <c r="B35" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>137239865</v>
       </c>
       <c r="B37" t="n">
-        <v>91582</v>
+        <v>91583</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>137239876</v>
       </c>
       <c r="B38" t="n">
-        <v>91582</v>
+        <v>91583</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>137239996</v>
       </c>
       <c r="B39" t="n">
-        <v>91582</v>
+        <v>91583</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>137237185</v>
       </c>
       <c r="B40" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>137239879</v>
       </c>
       <c r="B41" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>137273938</v>
       </c>
       <c r="B42" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>137241044</v>
       </c>
       <c r="B43" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>137240010</v>
       </c>
       <c r="B44" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>137241046</v>
       </c>
       <c r="B45" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137237186</v>
       </c>
       <c r="B46" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137239882</v>
       </c>
       <c r="B47" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137237181</v>
       </c>
       <c r="B48" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137237182</v>
       </c>
       <c r="B49" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137237188</v>
       </c>
       <c r="B50" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>137237257</v>
       </c>
       <c r="B51" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>137237176</v>
       </c>
       <c r="B52" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>137240154</v>
       </c>
       <c r="B53" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>137237178</v>
       </c>
       <c r="B54" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237190</v>
       </c>
       <c r="B55" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237260</v>
       </c>
       <c r="B56" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237261</v>
       </c>
       <c r="B57" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137237262</v>
       </c>
       <c r="B58" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137239881</v>
       </c>
       <c r="B59" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240151</v>
       </c>
       <c r="B60" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240152</v>
       </c>
       <c r="B61" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240153</v>
       </c>
       <c r="B62" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>137240155</v>
       </c>
       <c r="B64" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>137273930</v>
       </c>
       <c r="B65" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>137239870</v>
       </c>
       <c r="B66" t="n">
-        <v>93495</v>
+        <v>93496</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>137239995</v>
       </c>
       <c r="B67" t="n">
-        <v>93495</v>
+        <v>93496</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137240000</v>
       </c>
       <c r="B68" t="n">
-        <v>93495</v>
+        <v>93496</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137239871</v>
       </c>
       <c r="B69" t="n">
-        <v>93509</v>
+        <v>93510</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>137240002</v>
       </c>
       <c r="B70" t="n">
-        <v>93509</v>
+        <v>93510</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137237179</v>
       </c>
       <c r="B3" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137237193</v>
       </c>
       <c r="B4" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137241048</v>
       </c>
       <c r="B5" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>137241042</v>
       </c>
       <c r="B6" t="n">
-        <v>87477</v>
+        <v>87480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>137240150</v>
       </c>
       <c r="B8" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137237189</v>
       </c>
       <c r="B13" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>137239872</v>
       </c>
       <c r="B14" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>137239874</v>
       </c>
       <c r="B15" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>137239997</v>
       </c>
       <c r="B16" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137239999</v>
       </c>
       <c r="B17" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137240009</v>
       </c>
       <c r="B18" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137237180</v>
       </c>
       <c r="B19" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137237259</v>
       </c>
       <c r="B20" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>137237191</v>
       </c>
       <c r="B21" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>137237258</v>
       </c>
       <c r="B22" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>137241043</v>
       </c>
       <c r="B23" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>137273929</v>
       </c>
       <c r="B24" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>137273932</v>
       </c>
       <c r="B25" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137239866</v>
       </c>
       <c r="B26" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137239867</v>
       </c>
       <c r="B27" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>137241047</v>
       </c>
       <c r="B28" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>137273927</v>
       </c>
       <c r="B29" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>137273931</v>
       </c>
       <c r="B30" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>137239864</v>
       </c>
       <c r="B31" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137239869</v>
       </c>
       <c r="B32" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>137239994</v>
       </c>
       <c r="B33" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>137240171</v>
       </c>
       <c r="B34" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>137241045</v>
       </c>
       <c r="B35" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>137239865</v>
       </c>
       <c r="B37" t="n">
-        <v>91583</v>
+        <v>91586</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>137239876</v>
       </c>
       <c r="B38" t="n">
-        <v>91583</v>
+        <v>91586</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>137239996</v>
       </c>
       <c r="B39" t="n">
-        <v>91583</v>
+        <v>91586</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>137237185</v>
       </c>
       <c r="B40" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>137239879</v>
       </c>
       <c r="B41" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>137273938</v>
       </c>
       <c r="B42" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>137241044</v>
       </c>
       <c r="B43" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>137240010</v>
       </c>
       <c r="B44" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>137241046</v>
       </c>
       <c r="B45" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137237186</v>
       </c>
       <c r="B46" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137239882</v>
       </c>
       <c r="B47" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137237181</v>
       </c>
       <c r="B48" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137237182</v>
       </c>
       <c r="B49" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137237188</v>
       </c>
       <c r="B50" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>137237257</v>
       </c>
       <c r="B51" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>137237176</v>
       </c>
       <c r="B52" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>137240154</v>
       </c>
       <c r="B53" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>137237178</v>
       </c>
       <c r="B54" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237190</v>
       </c>
       <c r="B55" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237260</v>
       </c>
       <c r="B56" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237261</v>
       </c>
       <c r="B57" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137237262</v>
       </c>
       <c r="B58" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137239881</v>
       </c>
       <c r="B59" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240151</v>
       </c>
       <c r="B60" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240152</v>
       </c>
       <c r="B61" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240153</v>
       </c>
       <c r="B62" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>137240155</v>
       </c>
       <c r="B64" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>137273930</v>
       </c>
       <c r="B65" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>137239870</v>
       </c>
       <c r="B66" t="n">
-        <v>93496</v>
+        <v>93499</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>137239995</v>
       </c>
       <c r="B67" t="n">
-        <v>93496</v>
+        <v>93499</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137240000</v>
       </c>
       <c r="B68" t="n">
-        <v>93496</v>
+        <v>93499</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137239871</v>
       </c>
       <c r="B69" t="n">
-        <v>93510</v>
+        <v>93513</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>137240002</v>
       </c>
       <c r="B70" t="n">
-        <v>93510</v>
+        <v>93513</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 42411-2026 artfynd.xlsx
+++ b/artfynd/A 42411-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137237179</v>
       </c>
       <c r="B3" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137237193</v>
       </c>
       <c r="B4" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137241048</v>
       </c>
       <c r="B5" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>137241042</v>
       </c>
       <c r="B6" t="n">
-        <v>87480</v>
+        <v>87484</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>137240150</v>
       </c>
       <c r="B8" t="n">
-        <v>87536</v>
+        <v>87540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137237189</v>
       </c>
       <c r="B13" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>137239872</v>
       </c>
       <c r="B14" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>137239874</v>
       </c>
       <c r="B15" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>137239997</v>
       </c>
       <c r="B16" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137239999</v>
       </c>
       <c r="B17" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137240009</v>
       </c>
       <c r="B18" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137237180</v>
       </c>
       <c r="B19" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137237259</v>
       </c>
       <c r="B20" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>137237191</v>
       </c>
       <c r="B21" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>137237258</v>
       </c>
       <c r="B22" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>137241043</v>
       </c>
       <c r="B23" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>137273929</v>
       </c>
       <c r="B24" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>137273932</v>
       </c>
       <c r="B25" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137239866</v>
       </c>
       <c r="B26" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137239867</v>
       </c>
       <c r="B27" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>137241047</v>
       </c>
       <c r="B28" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>137273927</v>
       </c>
       <c r="B29" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>137273931</v>
       </c>
       <c r="B30" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>137239864</v>
       </c>
       <c r="B31" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137239869</v>
       </c>
       <c r="B32" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>137239994</v>
       </c>
       <c r="B33" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>137240171</v>
       </c>
       <c r="B34" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>137241045</v>
       </c>
       <c r="B35" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>137239865</v>
       </c>
       <c r="B37" t="n">
-        <v>91586</v>
+        <v>91590</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>137239876</v>
       </c>
       <c r="B38" t="n">
-        <v>91586</v>
+        <v>91590</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>137239996</v>
       </c>
       <c r="B39" t="n">
-        <v>91586</v>
+        <v>91590</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>137237185</v>
       </c>
       <c r="B40" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>137239879</v>
       </c>
       <c r="B41" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>137273938</v>
       </c>
       <c r="B42" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>137241044</v>
       </c>
       <c r="B43" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>137240010</v>
       </c>
       <c r="B44" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>137241046</v>
       </c>
       <c r="B45" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137237186</v>
       </c>
       <c r="B46" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137239882</v>
       </c>
       <c r="B47" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137237181</v>
       </c>
       <c r="B48" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137237182</v>
       </c>
       <c r="B49" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137237188</v>
       </c>
       <c r="B50" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>137237257</v>
       </c>
       <c r="B51" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>137237176</v>
       </c>
       <c r="B52" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>137240154</v>
       </c>
       <c r="B53" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>137237178</v>
       </c>
       <c r="B54" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237190</v>
       </c>
       <c r="B55" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237260</v>
       </c>
       <c r="B56" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237261</v>
       </c>
       <c r="B57" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137237262</v>
       </c>
       <c r="B58" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137239881</v>
       </c>
       <c r="B59" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240151</v>
       </c>
       <c r="B60" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240152</v>
       </c>
       <c r="B61" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240153</v>
       </c>
       <c r="B62" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>137240155</v>
       </c>
       <c r="B64" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>137273930</v>
       </c>
       <c r="B65" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>137239870</v>
       </c>
       <c r="B66" t="n">
-        <v>93499</v>
+        <v>93503</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>137239995</v>
       </c>
       <c r="B67" t="n">
-        <v>93499</v>
+        <v>93503</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137240000</v>
       </c>
       <c r="B68" t="n">
-        <v>93499</v>
+        <v>93503</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>137239871</v>
       </c>
       <c r="B69" t="n">
-        <v>93513</v>
+        <v>93517</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>137240002</v>
       </c>
       <c r="B70" t="n">
-        <v>93513</v>
+        <v>93517</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
